--- a/debug/excel_overviews/gpt-4.1_vs_Llama-3.1-8B-Instruct/phi-4/default/total_votes_file.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Llama-3.1-8B-Instruct/phi-4/default/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>164</v>
+        <v>181</v>
       </c>
       <c r="D2">
-        <v>113</v>
+        <v>158</v>
       </c>
       <c r="E2">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="G2">
-        <v>127</v>
+        <v>60</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>257</v>
+        <v>296</v>
       </c>
       <c r="D3">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="E3">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="G3">
-        <v>103</v>
+        <v>52</v>
       </c>
       <c r="H3">
         <v>426</v>
